--- a/保安管理/每日安保工作报告（模板）.xlsx
+++ b/保安管理/每日安保工作报告（模板）.xlsx
@@ -12,12 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
   <si>
     <t>每日安保工作报告</t>
   </si>
   <si>
-    <t>报告人：__________    日期：2026-____-____    天气：__________    当班时间：8:00 — 17:30    出勤：□正常  □请假  □调休（说明：__________）</t>
+    <t>报告人（保安）：__________    日期：2026-____-____    天气：__________    当班时间：8:00 — 17:30</t>
+  </si>
+  <si>
+    <t>保安出勤：□正常  □请假  □调休（说明：__________）    门岗协管（门卫）出勤：□正常  □请假  □调休（说明：__________）</t>
   </si>
   <si>
     <t>一、车位管理（8:00 — 8:30）</t>
@@ -74,7 +77,7 @@
     <t>下午补充巡查点位（如有）：</t>
   </si>
   <si>
-    <t>三、车辆进出与后备箱检查</t>
+    <t>三、车辆进出与后备箱检查（全天常态化 · 门卫执行 · 保安复核）</t>
   </si>
   <si>
     <t>今日进出车辆</t>
@@ -83,10 +86,10 @@
     <t>出：____ 辆</t>
   </si>
   <si>
-    <t>检查异常：□ 无  □ 有（说明：__________）</t>
-  </si>
-  <si>
-    <t>拒不配合：□ 无  □ 有（车牌：__________，□ 已上报总经办）</t>
+    <t>保安复核：□ 已复核登记完整性（每日至少 1 次）    检查异常：□ 无  □ 有（说明：__________）</t>
+  </si>
+  <si>
+    <t>拒不配合：□ 无  □ 有（车牌：__________，□ 已上报保安/总经办）</t>
   </si>
   <si>
     <t>四、监控与晚间录像抽查</t>
@@ -140,7 +143,10 @@
     <t>七、次日关注事项</t>
   </si>
   <si>
-    <t>报告人签字：__________</t>
+    <t>保安签字：__________</t>
+  </si>
+  <si>
+    <t>门岗协管签字：__________</t>
   </si>
   <si>
     <t>总经办接收：__________</t>
@@ -155,7 +161,7 @@
     <t>提交时间</t>
   </si>
   <si>
-    <t>每日 17:15 — 17:30 填写，17:30 前提交</t>
+    <t>每日 17:15 — 17:30 由保安汇总门岗登记后填写，17:30 前提交</t>
   </si>
   <si>
     <t>提交方式</t>
@@ -173,19 +179,19 @@
     <t>出勤填写</t>
   </si>
   <si>
-    <t>正常/请假/调休三选一；请假调休须提前一天向总经办申请</t>
+    <t>保安与门岗协管（门卫）分别填写出勤；请假调休须提前一天向总经办申请，两人错开</t>
   </si>
   <si>
     <t>四角巡查</t>
   </si>
   <si>
-    <t>东南→西南→东北→西北四角各拍 1 张带时间水印照片，当日发群</t>
-  </si>
-  <si>
-    <t>后备箱检查</t>
-  </si>
-  <si>
-    <t>所有出厂车辆必查（重点：螺栓、废铁、电缆、油品、工具），大货车/重型车辆必查</t>
+    <t>东南→西南→东北→西北四角各拍 1 张带时间水印照片，当日发群（保安执行）</t>
+  </si>
+  <si>
+    <t>车辆检查</t>
+  </si>
+  <si>
+    <t>全天常态化：车辆随到随登记随检查，门卫执行、保安每日复核 1 次；出厂车辆重点检查螺栓/废铁/电缆/油品/工具（721 教训）；拒不配合立即扣车上报</t>
   </si>
   <si>
     <t>录像抽查</t>
@@ -209,7 +215,7 @@
     <t>填写示例</t>
   </si>
   <si>
-    <t>2026-08-18 张XX 晴｜车位正常 处置1辆｜四角 9:05/9:28/9:50/10:15 已发群 西南角围挡松动已报修｜进出 15/12 辆 检查12辆｜监控正常16路 抽测4路｜16:40 拾荒1人已驱离｜事件：无｜次日：西南角围挡修复</t>
+    <t>2026-08-18 张XX(保安)/李XX(门卫) 晴｜车位正常 处置1辆｜四角 9:05/9:28/9:50/10:15 已发群 西南角围挡松动已报修｜进出 15/12 辆 检查12辆 门卫登记已复核｜监控正常16路 抽测4路｜16:40 拾荒1人已驱离｜事件：无｜次日：西南角围挡修复</t>
   </si>
 </sst>
 </file>
@@ -644,7 +650,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -665,7 +671,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -675,104 +681,98 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="F5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="E8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -782,13 +782,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -798,62 +798,64 @@
         <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -865,55 +867,55 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="E20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -925,25 +927,25 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -965,97 +967,97 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+    <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="B28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="C28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="D28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -1063,60 +1065,72 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="4" t="s">
+    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="38">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:F15"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="D30:F30"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="D36:F36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1134,90 +1148,90 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/保安管理/每日安保工作报告（模板）.xlsx
+++ b/保安管理/每日安保工作报告（模板）.xlsx
@@ -1,13 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrseven\Desktop\总经办文档\保安管理\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowWidth="27950" windowHeight="14080"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="日报" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="填写说明" state="visible" r:id="rId5"/>
+    <sheet name="日报" sheetId="1" r:id="rId1"/>
+    <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -149,7 +170,7 @@
     <t>门岗协管签字：__________</t>
   </si>
   <si>
-    <t>总经办接收：__________</t>
+    <t>行政部接收：__________</t>
   </si>
   <si>
     <t>项目</t>
@@ -221,31 +242,191 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="微软雅黑"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,16 +435,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -286,40 +655,326 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -641,17 +1296,16 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -661,435 +1315,435 @@
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:6">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:6">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:6">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:6">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:6">
+      <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" s="4" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="E8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:6">
+      <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:6">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:6">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:6">
+      <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:6">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:6">
+      <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:6">
+      <c r="A18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:6">
+      <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:6">
+      <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4" t="s">
+      <c r="B20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="E20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:6">
+      <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:6">
+      <c r="A22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:6">
+      <c r="A23" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:6">
+      <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:6">
+      <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:6">
+      <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:6">
+      <c r="A27" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" ht="20" customHeight="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" s="4" customFormat="1" ht="20" customHeight="1" spans="1:6">
+      <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:6">
+      <c r="A29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:6">
+      <c r="A30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:6">
+      <c r="A31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:6">
+      <c r="A32" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:6">
+      <c r="A33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:6">
+      <c r="A34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:6">
+      <c r="A36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="4" t="s">
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="38">
@@ -1133,109 +1787,112 @@
     <mergeCell ref="D36:F36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="34" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" ht="34" customHeight="1" spans="1:2">
+      <c r="A3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" ht="34" customHeight="1" spans="1:2">
+      <c r="A4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" ht="34" customHeight="1" spans="1:2">
+      <c r="A5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="34" customHeight="1" spans="1:2">
+      <c r="A6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" ht="34" customHeight="1" spans="1:2">
+      <c r="A7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="34" customHeight="1" spans="1:2">
+      <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" ht="34" customHeight="1" spans="1:2">
+      <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" ht="34" customHeight="1" spans="1:2">
+      <c r="A10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" ht="60" customHeight="1" spans="1:2">
+      <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>